--- a/business_analysis/AI/DailyChatFlow.xlsx
+++ b/business_analysis/AI/DailyChatFlow.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\WellBeingBuddy\business_analysis\ai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellbeingbuddy-anodiam\business_analysis\AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78348E1-6AF3-472C-A683-B365117B1B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23258" windowHeight="12458"/>
   </bookViews>
   <sheets>
     <sheet name="wellbeing_scores_2099_students" sheetId="1" r:id="rId1"/>
@@ -355,7 +354,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -550,7 +549,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -728,6 +727,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1018,7 +1023,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1071,6 +1076,9 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1104,8 +1112,11 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1427,52 +1438,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G373"/>
-  <sheetFormatPr defaultColWidth="29.44140625" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="29.46484375" defaultRowHeight="11.65" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="28.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.53125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="29.44140625" style="1"/>
+    <col min="5" max="5" width="19.1328125" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.53125" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="29.46484375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
+      <c r="B1" s="25"/>
       <c r="C1" s="16"/>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="19"/>
-    </row>
-    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="27" t="s">
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="19"/>
-      <c r="F2" s="18" t="s">
+      <c r="E2" s="20"/>
+      <c r="F2" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="21"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="28"/>
+      <c r="G2" s="20"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="22"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
@@ -1486,7 +1497,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" s="5" customFormat="1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1496,11 +1507,11 @@
       </c>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="30" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="10"/>
@@ -1510,11 +1521,11 @@
       <c r="E5" s="7"/>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="30" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="5">
@@ -1524,11 +1535,11 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" s="5" customFormat="1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="31" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="10"/>
@@ -1537,11 +1548,11 @@
       <c r="F7" s="8"/>
       <c r="G7" s="9"/>
     </row>
-    <row r="8" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="30" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="5">
@@ -1553,11 +1564,11 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="30" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="7"/>
@@ -1566,7 +1577,7 @@
       </c>
       <c r="G9" s="9"/>
     </row>
-    <row r="10" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
         <v>19</v>
       </c>
@@ -1584,7 +1595,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" s="5" customFormat="1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -1599,7 +1610,7 @@
       </c>
       <c r="G11" s="9"/>
     </row>
-    <row r="12" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
         <v>15</v>
       </c>
@@ -1616,7 +1627,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="5" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" s="5" customFormat="1" ht="34.9" x14ac:dyDescent="0.45">
       <c r="A13" s="12" t="s">
         <v>26</v>
       </c>
@@ -1627,7 +1638,7 @@
       <c r="E13" s="7"/>
       <c r="G13" s="9"/>
     </row>
-    <row r="14" spans="1:7" s="5" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" s="5" customFormat="1" ht="34.9" x14ac:dyDescent="0.45">
       <c r="A14" s="12" t="s">
         <v>28</v>
       </c>
@@ -1640,7 +1651,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" s="5" customFormat="1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
@@ -1654,7 +1665,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="5" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" s="5" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>9</v>
       </c>
@@ -1668,7 +1679,7 @@
       </c>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
         <v>15</v>
       </c>
@@ -1683,7 +1694,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="5" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" s="5" customFormat="1" ht="34.9" x14ac:dyDescent="0.45">
       <c r="A18" s="12" t="s">
         <v>37</v>
       </c>
@@ -1693,7 +1704,7 @@
       <c r="E18" s="7"/>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:7" s="5" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" s="5" customFormat="1" ht="34.9" x14ac:dyDescent="0.45">
       <c r="A19" s="12" t="s">
         <v>28</v>
       </c>
@@ -1707,11 +1718,11 @@
       </c>
       <c r="G19" s="7"/>
     </row>
-    <row r="20" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C20" s="5">
@@ -1722,7 +1733,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" s="5" customFormat="1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A21" s="12" t="s">
         <v>39</v>
       </c>
@@ -1735,7 +1746,7 @@
       </c>
       <c r="G21" s="7"/>
     </row>
-    <row r="22" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" s="5" customFormat="1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A22" s="12" t="s">
         <v>42</v>
       </c>
@@ -1750,7 +1761,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A23" s="12" t="s">
         <v>45</v>
       </c>
@@ -1760,7 +1771,7 @@
       <c r="E23" s="7"/>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" s="5" customFormat="1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A24" s="12" t="s">
         <v>47</v>
       </c>
@@ -1770,7 +1781,7 @@
       <c r="E24" s="7"/>
       <c r="G24" s="7"/>
     </row>
-    <row r="25" spans="1:7" s="5" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" s="5" customFormat="1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A25" s="12" t="s">
         <v>48</v>
       </c>
@@ -1784,7 +1795,7 @@
       </c>
       <c r="G25" s="7"/>
     </row>
-    <row r="26" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" s="5" customFormat="1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A26" s="12" t="s">
         <v>42</v>
       </c>
@@ -1799,7 +1810,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" s="5" customFormat="1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A27" s="12" t="s">
         <v>45</v>
       </c>
@@ -1809,7 +1820,7 @@
       <c r="E27" s="7"/>
       <c r="G27" s="7"/>
     </row>
-    <row r="28" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" s="5" customFormat="1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A28" s="12" t="s">
         <v>47</v>
       </c>
@@ -1819,7 +1830,7 @@
       <c r="E28" s="7"/>
       <c r="G28" s="7"/>
     </row>
-    <row r="29" spans="1:7" s="5" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" s="5" customFormat="1" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A29" s="12" t="s">
         <v>53</v>
       </c>
@@ -1832,1722 +1843,1722 @@
       <c r="E29" s="7"/>
       <c r="G29" s="7"/>
     </row>
-    <row r="30" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A30" s="4"/>
       <c r="E30" s="7"/>
       <c r="G30" s="7"/>
     </row>
-    <row r="31" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A31" s="4"/>
       <c r="E31" s="7"/>
       <c r="G31" s="7"/>
     </row>
-    <row r="32" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A32" s="4"/>
       <c r="E32" s="7"/>
       <c r="G32" s="7"/>
     </row>
-    <row r="33" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A33" s="4"/>
       <c r="E33" s="7"/>
       <c r="G33" s="7"/>
     </row>
-    <row r="34" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A34" s="4"/>
       <c r="E34" s="7"/>
       <c r="G34" s="7"/>
     </row>
-    <row r="35" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A35" s="4"/>
       <c r="E35" s="7"/>
       <c r="G35" s="7"/>
     </row>
-    <row r="36" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A36" s="4"/>
       <c r="E36" s="7"/>
       <c r="G36" s="7"/>
     </row>
-    <row r="37" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A37" s="4"/>
       <c r="E37" s="7"/>
       <c r="G37" s="7"/>
     </row>
-    <row r="38" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A38" s="4"/>
       <c r="E38" s="7"/>
       <c r="G38" s="7"/>
     </row>
-    <row r="39" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A39" s="4"/>
       <c r="E39" s="7"/>
       <c r="G39" s="7"/>
     </row>
-    <row r="40" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A40" s="4"/>
       <c r="E40" s="7"/>
       <c r="G40" s="7"/>
     </row>
-    <row r="41" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A41" s="4"/>
       <c r="E41" s="7"/>
       <c r="G41" s="7"/>
     </row>
-    <row r="42" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A42" s="4"/>
       <c r="E42" s="7"/>
       <c r="G42" s="7"/>
     </row>
-    <row r="43" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A43" s="4"/>
       <c r="E43" s="7"/>
       <c r="G43" s="7"/>
     </row>
-    <row r="44" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A44" s="4"/>
       <c r="E44" s="7"/>
       <c r="G44" s="7"/>
     </row>
-    <row r="45" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A45" s="4"/>
       <c r="E45" s="7"/>
       <c r="G45" s="7"/>
     </row>
-    <row r="46" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A46" s="4"/>
       <c r="E46" s="7"/>
       <c r="G46" s="7"/>
     </row>
-    <row r="47" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A47" s="4"/>
       <c r="E47" s="7"/>
       <c r="G47" s="7"/>
     </row>
-    <row r="48" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A48" s="4"/>
       <c r="E48" s="7"/>
       <c r="G48" s="7"/>
     </row>
-    <row r="49" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A49" s="4"/>
       <c r="E49" s="7"/>
       <c r="G49" s="7"/>
     </row>
-    <row r="50" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A50" s="4"/>
       <c r="E50" s="7"/>
       <c r="G50" s="7"/>
     </row>
-    <row r="51" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A51" s="4"/>
       <c r="E51" s="7"/>
       <c r="G51" s="7"/>
     </row>
-    <row r="52" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A52" s="4"/>
       <c r="E52" s="7"/>
       <c r="G52" s="7"/>
     </row>
-    <row r="53" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A53" s="4"/>
       <c r="E53" s="7"/>
       <c r="G53" s="7"/>
     </row>
-    <row r="54" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A54" s="4"/>
       <c r="E54" s="7"/>
       <c r="G54" s="7"/>
     </row>
-    <row r="55" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A55" s="4"/>
       <c r="E55" s="7"/>
       <c r="G55" s="7"/>
     </row>
-    <row r="56" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A56" s="4"/>
       <c r="E56" s="7"/>
       <c r="G56" s="7"/>
     </row>
-    <row r="57" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A57" s="4"/>
       <c r="E57" s="7"/>
       <c r="G57" s="7"/>
     </row>
-    <row r="58" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A58" s="4"/>
       <c r="E58" s="7"/>
       <c r="G58" s="7"/>
     </row>
-    <row r="59" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A59" s="4"/>
       <c r="E59" s="7"/>
       <c r="G59" s="7"/>
     </row>
-    <row r="60" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A60" s="4"/>
       <c r="E60" s="7"/>
       <c r="G60" s="7"/>
     </row>
-    <row r="61" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A61" s="4"/>
       <c r="E61" s="7"/>
       <c r="G61" s="7"/>
     </row>
-    <row r="62" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A62" s="4"/>
       <c r="E62" s="7"/>
       <c r="G62" s="7"/>
     </row>
-    <row r="63" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A63" s="4"/>
       <c r="E63" s="7"/>
       <c r="G63" s="7"/>
     </row>
-    <row r="64" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A64" s="4"/>
       <c r="E64" s="7"/>
       <c r="G64" s="7"/>
     </row>
-    <row r="65" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A65" s="4"/>
       <c r="E65" s="7"/>
       <c r="G65" s="7"/>
     </row>
-    <row r="66" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A66" s="4"/>
       <c r="E66" s="7"/>
       <c r="G66" s="7"/>
     </row>
-    <row r="67" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A67" s="4"/>
       <c r="E67" s="7"/>
       <c r="G67" s="7"/>
     </row>
-    <row r="68" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A68" s="4"/>
       <c r="E68" s="7"/>
       <c r="G68" s="7"/>
     </row>
-    <row r="69" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A69" s="4"/>
       <c r="E69" s="7"/>
       <c r="G69" s="7"/>
     </row>
-    <row r="70" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A70" s="4"/>
       <c r="E70" s="7"/>
       <c r="G70" s="7"/>
     </row>
-    <row r="71" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A71" s="4"/>
       <c r="E71" s="7"/>
       <c r="G71" s="7"/>
     </row>
-    <row r="72" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A72" s="4"/>
       <c r="E72" s="7"/>
       <c r="G72" s="7"/>
     </row>
-    <row r="73" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A73" s="4"/>
       <c r="E73" s="7"/>
       <c r="G73" s="7"/>
     </row>
-    <row r="74" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A74" s="4"/>
       <c r="E74" s="7"/>
       <c r="G74" s="7"/>
     </row>
-    <row r="75" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A75" s="4"/>
       <c r="E75" s="7"/>
       <c r="G75" s="7"/>
     </row>
-    <row r="76" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A76" s="4"/>
       <c r="E76" s="7"/>
       <c r="G76" s="7"/>
     </row>
-    <row r="77" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A77" s="4"/>
       <c r="E77" s="7"/>
       <c r="G77" s="7"/>
     </row>
-    <row r="78" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A78" s="4"/>
       <c r="E78" s="7"/>
       <c r="G78" s="7"/>
     </row>
-    <row r="79" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A79" s="4"/>
       <c r="E79" s="7"/>
       <c r="G79" s="7"/>
     </row>
-    <row r="80" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A80" s="4"/>
       <c r="E80" s="7"/>
       <c r="G80" s="7"/>
     </row>
-    <row r="81" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A81" s="4"/>
       <c r="E81" s="7"/>
       <c r="G81" s="7"/>
     </row>
-    <row r="82" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A82" s="4"/>
       <c r="E82" s="7"/>
       <c r="G82" s="7"/>
     </row>
-    <row r="83" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A83" s="4"/>
       <c r="E83" s="7"/>
       <c r="G83" s="7"/>
     </row>
-    <row r="84" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A84" s="4"/>
       <c r="E84" s="7"/>
       <c r="G84" s="7"/>
     </row>
-    <row r="85" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A85" s="4"/>
       <c r="E85" s="7"/>
       <c r="G85" s="7"/>
     </row>
-    <row r="86" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A86" s="4"/>
       <c r="E86" s="7"/>
       <c r="G86" s="7"/>
     </row>
-    <row r="87" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A87" s="4"/>
       <c r="E87" s="7"/>
       <c r="G87" s="7"/>
     </row>
-    <row r="88" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A88" s="4"/>
       <c r="E88" s="7"/>
       <c r="G88" s="7"/>
     </row>
-    <row r="89" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A89" s="4"/>
       <c r="E89" s="7"/>
       <c r="G89" s="7"/>
     </row>
-    <row r="90" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A90" s="4"/>
       <c r="E90" s="7"/>
       <c r="G90" s="7"/>
     </row>
-    <row r="91" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A91" s="4"/>
       <c r="E91" s="7"/>
       <c r="G91" s="7"/>
     </row>
-    <row r="92" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A92" s="4"/>
       <c r="E92" s="7"/>
       <c r="G92" s="7"/>
     </row>
-    <row r="93" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A93" s="4"/>
       <c r="E93" s="7"/>
       <c r="G93" s="7"/>
     </row>
-    <row r="94" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A94" s="4"/>
       <c r="E94" s="7"/>
       <c r="G94" s="7"/>
     </row>
-    <row r="95" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A95" s="4"/>
       <c r="E95" s="7"/>
       <c r="G95" s="7"/>
     </row>
-    <row r="96" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A96" s="4"/>
       <c r="E96" s="7"/>
       <c r="G96" s="7"/>
     </row>
-    <row r="97" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A97" s="4"/>
       <c r="E97" s="7"/>
       <c r="G97" s="7"/>
     </row>
-    <row r="98" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A98" s="4"/>
       <c r="E98" s="7"/>
       <c r="G98" s="7"/>
     </row>
-    <row r="99" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A99" s="4"/>
       <c r="E99" s="7"/>
       <c r="G99" s="7"/>
     </row>
-    <row r="100" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A100" s="4"/>
       <c r="E100" s="7"/>
       <c r="G100" s="7"/>
     </row>
-    <row r="101" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A101" s="4"/>
       <c r="E101" s="7"/>
       <c r="G101" s="7"/>
     </row>
-    <row r="102" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A102" s="4"/>
       <c r="E102" s="7"/>
       <c r="G102" s="7"/>
     </row>
-    <row r="103" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A103" s="4"/>
       <c r="E103" s="7"/>
       <c r="G103" s="7"/>
     </row>
-    <row r="104" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A104" s="4"/>
       <c r="E104" s="7"/>
       <c r="G104" s="7"/>
     </row>
-    <row r="105" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A105" s="4"/>
       <c r="E105" s="7"/>
       <c r="G105" s="7"/>
     </row>
-    <row r="106" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A106" s="4"/>
       <c r="E106" s="7"/>
       <c r="G106" s="7"/>
     </row>
-    <row r="107" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A107" s="4"/>
       <c r="E107" s="7"/>
       <c r="G107" s="7"/>
     </row>
-    <row r="108" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A108" s="4"/>
       <c r="E108" s="7"/>
       <c r="G108" s="7"/>
     </row>
-    <row r="109" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A109" s="4"/>
       <c r="E109" s="7"/>
       <c r="G109" s="7"/>
     </row>
-    <row r="110" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A110" s="4"/>
       <c r="E110" s="7"/>
       <c r="G110" s="7"/>
     </row>
-    <row r="111" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A111" s="4"/>
       <c r="E111" s="7"/>
       <c r="G111" s="7"/>
     </row>
-    <row r="112" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A112" s="4"/>
       <c r="E112" s="7"/>
       <c r="G112" s="7"/>
     </row>
-    <row r="113" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A113" s="4"/>
       <c r="E113" s="7"/>
       <c r="G113" s="7"/>
     </row>
-    <row r="114" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A114" s="4"/>
       <c r="E114" s="7"/>
       <c r="G114" s="7"/>
     </row>
-    <row r="115" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A115" s="4"/>
       <c r="E115" s="7"/>
       <c r="G115" s="7"/>
     </row>
-    <row r="116" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A116" s="4"/>
       <c r="E116" s="7"/>
       <c r="G116" s="7"/>
     </row>
-    <row r="117" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A117" s="4"/>
       <c r="E117" s="7"/>
       <c r="G117" s="7"/>
     </row>
-    <row r="118" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A118" s="4"/>
       <c r="E118" s="7"/>
       <c r="G118" s="7"/>
     </row>
-    <row r="119" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A119" s="4"/>
       <c r="E119" s="7"/>
       <c r="G119" s="7"/>
     </row>
-    <row r="120" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A120" s="4"/>
       <c r="E120" s="7"/>
       <c r="G120" s="7"/>
     </row>
-    <row r="121" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A121" s="4"/>
       <c r="E121" s="7"/>
       <c r="G121" s="7"/>
     </row>
-    <row r="122" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A122" s="4"/>
       <c r="E122" s="7"/>
       <c r="G122" s="7"/>
     </row>
-    <row r="123" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A123" s="4"/>
       <c r="E123" s="7"/>
       <c r="G123" s="7"/>
     </row>
-    <row r="124" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A124" s="4"/>
       <c r="E124" s="7"/>
       <c r="G124" s="7"/>
     </row>
-    <row r="125" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A125" s="4"/>
       <c r="E125" s="7"/>
       <c r="G125" s="7"/>
     </row>
-    <row r="126" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A126" s="4"/>
       <c r="E126" s="7"/>
       <c r="G126" s="7"/>
     </row>
-    <row r="127" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A127" s="4"/>
       <c r="E127" s="7"/>
       <c r="G127" s="7"/>
     </row>
-    <row r="128" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A128" s="4"/>
       <c r="E128" s="7"/>
       <c r="G128" s="7"/>
     </row>
-    <row r="129" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A129" s="4"/>
       <c r="E129" s="7"/>
       <c r="G129" s="7"/>
     </row>
-    <row r="130" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A130" s="4"/>
       <c r="E130" s="7"/>
       <c r="G130" s="7"/>
     </row>
-    <row r="131" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A131" s="4"/>
       <c r="E131" s="7"/>
       <c r="G131" s="7"/>
     </row>
-    <row r="132" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A132" s="4"/>
       <c r="E132" s="7"/>
       <c r="G132" s="7"/>
     </row>
-    <row r="133" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A133" s="4"/>
       <c r="E133" s="7"/>
       <c r="G133" s="7"/>
     </row>
-    <row r="134" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A134" s="4"/>
       <c r="E134" s="7"/>
       <c r="G134" s="7"/>
     </row>
-    <row r="135" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A135" s="4"/>
       <c r="E135" s="7"/>
       <c r="G135" s="7"/>
     </row>
-    <row r="136" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A136" s="4"/>
       <c r="E136" s="7"/>
       <c r="G136" s="7"/>
     </row>
-    <row r="137" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A137" s="4"/>
       <c r="E137" s="7"/>
       <c r="G137" s="7"/>
     </row>
-    <row r="138" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A138" s="4"/>
       <c r="E138" s="7"/>
       <c r="G138" s="7"/>
     </row>
-    <row r="139" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A139" s="4"/>
       <c r="E139" s="7"/>
       <c r="G139" s="7"/>
     </row>
-    <row r="140" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A140" s="4"/>
       <c r="E140" s="7"/>
       <c r="G140" s="7"/>
     </row>
-    <row r="141" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A141" s="4"/>
       <c r="E141" s="7"/>
       <c r="G141" s="7"/>
     </row>
-    <row r="142" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A142" s="4"/>
       <c r="E142" s="7"/>
       <c r="G142" s="7"/>
     </row>
-    <row r="143" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A143" s="4"/>
       <c r="E143" s="7"/>
       <c r="G143" s="7"/>
     </row>
-    <row r="144" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A144" s="4"/>
       <c r="E144" s="7"/>
       <c r="G144" s="7"/>
     </row>
-    <row r="145" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A145" s="4"/>
       <c r="E145" s="7"/>
       <c r="G145" s="7"/>
     </row>
-    <row r="146" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A146" s="4"/>
       <c r="E146" s="7"/>
       <c r="G146" s="7"/>
     </row>
-    <row r="147" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A147" s="4"/>
       <c r="E147" s="7"/>
       <c r="G147" s="7"/>
     </row>
-    <row r="148" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A148" s="4"/>
       <c r="E148" s="7"/>
       <c r="G148" s="7"/>
     </row>
-    <row r="149" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A149" s="4"/>
       <c r="E149" s="7"/>
       <c r="G149" s="7"/>
     </row>
-    <row r="150" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A150" s="4"/>
       <c r="E150" s="7"/>
       <c r="G150" s="7"/>
     </row>
-    <row r="151" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A151" s="4"/>
       <c r="E151" s="7"/>
       <c r="G151" s="7"/>
     </row>
-    <row r="152" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A152" s="4"/>
       <c r="E152" s="7"/>
       <c r="G152" s="7"/>
     </row>
-    <row r="153" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A153" s="4"/>
       <c r="E153" s="7"/>
       <c r="G153" s="7"/>
     </row>
-    <row r="154" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A154" s="4"/>
       <c r="E154" s="7"/>
       <c r="G154" s="7"/>
     </row>
-    <row r="155" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A155" s="4"/>
       <c r="E155" s="7"/>
       <c r="G155" s="7"/>
     </row>
-    <row r="156" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A156" s="4"/>
       <c r="E156" s="7"/>
       <c r="G156" s="7"/>
     </row>
-    <row r="157" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A157" s="4"/>
       <c r="E157" s="7"/>
       <c r="G157" s="7"/>
     </row>
-    <row r="158" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A158" s="4"/>
       <c r="E158" s="7"/>
       <c r="G158" s="7"/>
     </row>
-    <row r="159" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A159" s="4"/>
       <c r="E159" s="7"/>
       <c r="G159" s="7"/>
     </row>
-    <row r="160" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A160" s="4"/>
       <c r="E160" s="7"/>
       <c r="G160" s="7"/>
     </row>
-    <row r="161" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A161" s="4"/>
       <c r="E161" s="7"/>
       <c r="G161" s="7"/>
     </row>
-    <row r="162" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A162" s="4"/>
       <c r="E162" s="7"/>
       <c r="G162" s="7"/>
     </row>
-    <row r="163" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A163" s="4"/>
       <c r="E163" s="7"/>
       <c r="G163" s="7"/>
     </row>
-    <row r="164" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A164" s="4"/>
       <c r="E164" s="7"/>
       <c r="G164" s="7"/>
     </row>
-    <row r="165" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A165" s="4"/>
       <c r="E165" s="7"/>
       <c r="G165" s="7"/>
     </row>
-    <row r="166" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A166" s="4"/>
       <c r="E166" s="7"/>
       <c r="G166" s="7"/>
     </row>
-    <row r="167" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A167" s="4"/>
       <c r="E167" s="7"/>
       <c r="G167" s="7"/>
     </row>
-    <row r="168" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A168" s="4"/>
       <c r="E168" s="7"/>
       <c r="G168" s="7"/>
     </row>
-    <row r="169" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A169" s="4"/>
       <c r="E169" s="7"/>
       <c r="G169" s="7"/>
     </row>
-    <row r="170" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A170" s="4"/>
       <c r="E170" s="7"/>
       <c r="G170" s="7"/>
     </row>
-    <row r="171" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A171" s="4"/>
       <c r="E171" s="7"/>
       <c r="G171" s="7"/>
     </row>
-    <row r="172" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A172" s="4"/>
       <c r="E172" s="7"/>
       <c r="G172" s="7"/>
     </row>
-    <row r="173" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A173" s="4"/>
       <c r="E173" s="7"/>
       <c r="G173" s="7"/>
     </row>
-    <row r="174" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A174" s="4"/>
       <c r="E174" s="7"/>
       <c r="G174" s="7"/>
     </row>
-    <row r="175" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A175" s="4"/>
       <c r="E175" s="7"/>
       <c r="G175" s="7"/>
     </row>
-    <row r="176" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A176" s="4"/>
       <c r="E176" s="7"/>
       <c r="G176" s="7"/>
     </row>
-    <row r="177" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A177" s="4"/>
       <c r="E177" s="7"/>
       <c r="G177" s="7"/>
     </row>
-    <row r="178" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A178" s="4"/>
       <c r="E178" s="7"/>
       <c r="G178" s="7"/>
     </row>
-    <row r="179" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A179" s="4"/>
       <c r="E179" s="7"/>
       <c r="G179" s="7"/>
     </row>
-    <row r="180" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A180" s="4"/>
       <c r="E180" s="7"/>
       <c r="G180" s="7"/>
     </row>
-    <row r="181" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A181" s="4"/>
       <c r="E181" s="7"/>
       <c r="G181" s="7"/>
     </row>
-    <row r="182" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A182" s="4"/>
       <c r="E182" s="7"/>
       <c r="G182" s="7"/>
     </row>
-    <row r="183" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A183" s="4"/>
       <c r="E183" s="7"/>
       <c r="G183" s="7"/>
     </row>
-    <row r="184" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A184" s="4"/>
       <c r="E184" s="7"/>
       <c r="G184" s="7"/>
     </row>
-    <row r="185" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A185" s="4"/>
       <c r="E185" s="7"/>
       <c r="G185" s="7"/>
     </row>
-    <row r="186" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A186" s="4"/>
       <c r="E186" s="7"/>
       <c r="G186" s="7"/>
     </row>
-    <row r="187" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A187" s="4"/>
       <c r="E187" s="7"/>
       <c r="G187" s="7"/>
     </row>
-    <row r="188" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A188" s="4"/>
       <c r="E188" s="7"/>
       <c r="G188" s="7"/>
     </row>
-    <row r="189" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A189" s="4"/>
       <c r="E189" s="7"/>
       <c r="G189" s="7"/>
     </row>
-    <row r="190" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A190" s="4"/>
       <c r="E190" s="7"/>
       <c r="G190" s="7"/>
     </row>
-    <row r="191" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A191" s="4"/>
       <c r="E191" s="7"/>
       <c r="G191" s="7"/>
     </row>
-    <row r="192" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A192" s="4"/>
       <c r="E192" s="7"/>
       <c r="G192" s="7"/>
     </row>
-    <row r="193" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A193" s="4"/>
       <c r="E193" s="7"/>
       <c r="G193" s="7"/>
     </row>
-    <row r="194" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A194" s="4"/>
       <c r="E194" s="7"/>
       <c r="G194" s="7"/>
     </row>
-    <row r="195" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A195" s="4"/>
       <c r="E195" s="7"/>
       <c r="G195" s="7"/>
     </row>
-    <row r="196" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A196" s="4"/>
       <c r="E196" s="7"/>
       <c r="G196" s="7"/>
     </row>
-    <row r="197" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A197" s="4"/>
       <c r="E197" s="7"/>
       <c r="G197" s="7"/>
     </row>
-    <row r="198" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A198" s="4"/>
       <c r="E198" s="7"/>
       <c r="G198" s="7"/>
     </row>
-    <row r="199" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A199" s="4"/>
       <c r="E199" s="7"/>
       <c r="G199" s="7"/>
     </row>
-    <row r="200" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A200" s="4"/>
       <c r="E200" s="7"/>
       <c r="G200" s="7"/>
     </row>
-    <row r="201" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A201" s="4"/>
       <c r="E201" s="7"/>
       <c r="G201" s="7"/>
     </row>
-    <row r="202" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A202" s="4"/>
       <c r="E202" s="7"/>
       <c r="G202" s="7"/>
     </row>
-    <row r="203" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A203" s="4"/>
       <c r="E203" s="7"/>
       <c r="G203" s="7"/>
     </row>
-    <row r="204" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A204" s="4"/>
       <c r="E204" s="7"/>
       <c r="G204" s="7"/>
     </row>
-    <row r="205" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A205" s="4"/>
       <c r="E205" s="7"/>
       <c r="G205" s="7"/>
     </row>
-    <row r="206" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A206" s="4"/>
       <c r="E206" s="7"/>
       <c r="G206" s="7"/>
     </row>
-    <row r="207" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A207" s="4"/>
       <c r="E207" s="7"/>
       <c r="G207" s="7"/>
     </row>
-    <row r="208" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A208" s="4"/>
       <c r="E208" s="7"/>
       <c r="G208" s="7"/>
     </row>
-    <row r="209" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A209" s="4"/>
       <c r="E209" s="7"/>
       <c r="G209" s="7"/>
     </row>
-    <row r="210" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A210" s="4"/>
       <c r="E210" s="7"/>
       <c r="G210" s="7"/>
     </row>
-    <row r="211" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A211" s="4"/>
       <c r="E211" s="7"/>
       <c r="G211" s="7"/>
     </row>
-    <row r="212" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A212" s="4"/>
       <c r="E212" s="7"/>
       <c r="G212" s="7"/>
     </row>
-    <row r="213" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A213" s="4"/>
       <c r="E213" s="7"/>
       <c r="G213" s="7"/>
     </row>
-    <row r="214" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A214" s="4"/>
       <c r="E214" s="7"/>
       <c r="G214" s="7"/>
     </row>
-    <row r="215" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A215" s="4"/>
       <c r="E215" s="7"/>
       <c r="G215" s="7"/>
     </row>
-    <row r="216" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A216" s="4"/>
       <c r="E216" s="7"/>
       <c r="G216" s="7"/>
     </row>
-    <row r="217" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A217" s="4"/>
       <c r="E217" s="7"/>
       <c r="G217" s="7"/>
     </row>
-    <row r="218" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A218" s="4"/>
       <c r="E218" s="7"/>
       <c r="G218" s="7"/>
     </row>
-    <row r="219" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A219" s="4"/>
       <c r="E219" s="7"/>
       <c r="G219" s="7"/>
     </row>
-    <row r="220" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A220" s="4"/>
       <c r="E220" s="7"/>
       <c r="G220" s="7"/>
     </row>
-    <row r="221" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A221" s="4"/>
       <c r="E221" s="7"/>
       <c r="G221" s="7"/>
     </row>
-    <row r="222" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A222" s="4"/>
       <c r="E222" s="7"/>
       <c r="G222" s="7"/>
     </row>
-    <row r="223" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A223" s="4"/>
       <c r="E223" s="7"/>
       <c r="G223" s="7"/>
     </row>
-    <row r="224" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A224" s="4"/>
       <c r="E224" s="7"/>
       <c r="G224" s="7"/>
     </row>
-    <row r="225" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A225" s="4"/>
       <c r="E225" s="7"/>
       <c r="G225" s="7"/>
     </row>
-    <row r="226" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A226" s="4"/>
       <c r="E226" s="7"/>
       <c r="G226" s="7"/>
     </row>
-    <row r="227" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A227" s="4"/>
       <c r="E227" s="7"/>
       <c r="G227" s="7"/>
     </row>
-    <row r="228" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A228" s="4"/>
       <c r="E228" s="7"/>
       <c r="G228" s="7"/>
     </row>
-    <row r="229" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A229" s="4"/>
       <c r="E229" s="7"/>
       <c r="G229" s="7"/>
     </row>
-    <row r="230" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A230" s="4"/>
       <c r="E230" s="7"/>
       <c r="G230" s="7"/>
     </row>
-    <row r="231" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A231" s="4"/>
       <c r="E231" s="7"/>
       <c r="G231" s="7"/>
     </row>
-    <row r="232" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A232" s="4"/>
       <c r="E232" s="7"/>
       <c r="G232" s="7"/>
     </row>
-    <row r="233" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A233" s="4"/>
       <c r="E233" s="7"/>
       <c r="G233" s="7"/>
     </row>
-    <row r="234" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A234" s="4"/>
       <c r="E234" s="7"/>
       <c r="G234" s="7"/>
     </row>
-    <row r="235" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A235" s="4"/>
       <c r="E235" s="7"/>
       <c r="G235" s="7"/>
     </row>
-    <row r="236" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A236" s="4"/>
       <c r="E236" s="7"/>
       <c r="G236" s="7"/>
     </row>
-    <row r="237" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A237" s="4"/>
       <c r="E237" s="7"/>
       <c r="G237" s="7"/>
     </row>
-    <row r="238" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A238" s="4"/>
       <c r="E238" s="7"/>
       <c r="G238" s="7"/>
     </row>
-    <row r="239" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A239" s="4"/>
       <c r="E239" s="7"/>
       <c r="G239" s="7"/>
     </row>
-    <row r="240" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A240" s="4"/>
       <c r="E240" s="7"/>
       <c r="G240" s="7"/>
     </row>
-    <row r="241" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A241" s="4"/>
       <c r="E241" s="7"/>
       <c r="G241" s="7"/>
     </row>
-    <row r="242" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A242" s="4"/>
       <c r="E242" s="7"/>
       <c r="G242" s="7"/>
     </row>
-    <row r="243" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A243" s="4"/>
       <c r="E243" s="7"/>
       <c r="G243" s="7"/>
     </row>
-    <row r="244" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A244" s="4"/>
       <c r="E244" s="7"/>
       <c r="G244" s="7"/>
     </row>
-    <row r="245" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A245" s="4"/>
       <c r="E245" s="7"/>
       <c r="G245" s="7"/>
     </row>
-    <row r="246" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A246" s="4"/>
       <c r="E246" s="7"/>
       <c r="G246" s="7"/>
     </row>
-    <row r="247" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A247" s="4"/>
       <c r="E247" s="7"/>
       <c r="G247" s="7"/>
     </row>
-    <row r="248" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A248" s="4"/>
       <c r="E248" s="7"/>
       <c r="G248" s="7"/>
     </row>
-    <row r="249" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A249" s="4"/>
       <c r="E249" s="7"/>
       <c r="G249" s="7"/>
     </row>
-    <row r="250" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A250" s="4"/>
       <c r="E250" s="7"/>
       <c r="G250" s="7"/>
     </row>
-    <row r="251" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A251" s="4"/>
       <c r="E251" s="7"/>
       <c r="G251" s="7"/>
     </row>
-    <row r="252" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A252" s="4"/>
       <c r="E252" s="7"/>
       <c r="G252" s="7"/>
     </row>
-    <row r="253" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A253" s="4"/>
       <c r="E253" s="7"/>
       <c r="G253" s="7"/>
     </row>
-    <row r="254" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A254" s="4"/>
       <c r="E254" s="7"/>
       <c r="G254" s="7"/>
     </row>
-    <row r="255" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A255" s="4"/>
       <c r="E255" s="7"/>
       <c r="G255" s="7"/>
     </row>
-    <row r="256" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A256" s="4"/>
       <c r="E256" s="7"/>
       <c r="G256" s="7"/>
     </row>
-    <row r="257" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A257" s="4"/>
       <c r="E257" s="7"/>
       <c r="G257" s="7"/>
     </row>
-    <row r="258" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A258" s="4"/>
       <c r="E258" s="7"/>
       <c r="G258" s="7"/>
     </row>
-    <row r="259" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A259" s="4"/>
       <c r="E259" s="7"/>
       <c r="G259" s="7"/>
     </row>
-    <row r="260" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A260" s="4"/>
       <c r="E260" s="7"/>
       <c r="G260" s="7"/>
     </row>
-    <row r="261" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A261" s="4"/>
       <c r="E261" s="7"/>
       <c r="G261" s="7"/>
     </row>
-    <row r="262" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A262" s="4"/>
       <c r="E262" s="7"/>
       <c r="G262" s="7"/>
     </row>
-    <row r="263" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A263" s="4"/>
       <c r="E263" s="7"/>
       <c r="G263" s="7"/>
     </row>
-    <row r="264" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A264" s="4"/>
       <c r="E264" s="7"/>
       <c r="G264" s="7"/>
     </row>
-    <row r="265" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A265" s="4"/>
       <c r="E265" s="7"/>
       <c r="G265" s="7"/>
     </row>
-    <row r="266" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A266" s="4"/>
       <c r="E266" s="7"/>
       <c r="G266" s="7"/>
     </row>
-    <row r="267" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A267" s="4"/>
       <c r="E267" s="7"/>
       <c r="G267" s="7"/>
     </row>
-    <row r="268" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A268" s="4"/>
       <c r="E268" s="7"/>
       <c r="G268" s="7"/>
     </row>
-    <row r="269" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A269" s="4"/>
       <c r="E269" s="7"/>
       <c r="G269" s="7"/>
     </row>
-    <row r="270" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A270" s="4"/>
       <c r="E270" s="7"/>
       <c r="G270" s="7"/>
     </row>
-    <row r="271" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A271" s="4"/>
       <c r="E271" s="7"/>
       <c r="G271" s="7"/>
     </row>
-    <row r="272" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A272" s="4"/>
       <c r="E272" s="7"/>
       <c r="G272" s="7"/>
     </row>
-    <row r="273" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A273" s="4"/>
       <c r="E273" s="7"/>
       <c r="G273" s="7"/>
     </row>
-    <row r="274" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A274" s="4"/>
       <c r="E274" s="7"/>
       <c r="G274" s="7"/>
     </row>
-    <row r="275" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A275" s="4"/>
       <c r="E275" s="7"/>
       <c r="G275" s="7"/>
     </row>
-    <row r="276" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A276" s="4"/>
       <c r="E276" s="7"/>
       <c r="G276" s="7"/>
     </row>
-    <row r="277" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A277" s="4"/>
       <c r="E277" s="7"/>
       <c r="G277" s="7"/>
     </row>
-    <row r="278" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A278" s="4"/>
       <c r="E278" s="7"/>
       <c r="G278" s="7"/>
     </row>
-    <row r="279" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A279" s="4"/>
       <c r="E279" s="7"/>
       <c r="G279" s="7"/>
     </row>
-    <row r="280" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A280" s="4"/>
       <c r="E280" s="7"/>
       <c r="G280" s="7"/>
     </row>
-    <row r="281" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A281" s="4"/>
       <c r="E281" s="7"/>
       <c r="G281" s="7"/>
     </row>
-    <row r="282" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A282" s="4"/>
       <c r="E282" s="7"/>
       <c r="G282" s="7"/>
     </row>
-    <row r="283" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A283" s="4"/>
       <c r="E283" s="7"/>
       <c r="G283" s="7"/>
     </row>
-    <row r="284" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A284" s="4"/>
       <c r="E284" s="7"/>
       <c r="G284" s="7"/>
     </row>
-    <row r="285" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A285" s="4"/>
       <c r="E285" s="7"/>
       <c r="G285" s="7"/>
     </row>
-    <row r="286" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A286" s="4"/>
       <c r="E286" s="7"/>
       <c r="G286" s="7"/>
     </row>
-    <row r="287" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A287" s="4"/>
       <c r="E287" s="7"/>
       <c r="G287" s="7"/>
     </row>
-    <row r="288" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A288" s="4"/>
       <c r="E288" s="7"/>
       <c r="G288" s="7"/>
     </row>
-    <row r="289" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A289" s="4"/>
       <c r="E289" s="7"/>
       <c r="G289" s="7"/>
     </row>
-    <row r="290" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A290" s="4"/>
       <c r="E290" s="7"/>
       <c r="G290" s="7"/>
     </row>
-    <row r="291" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A291" s="4"/>
       <c r="E291" s="7"/>
       <c r="G291" s="7"/>
     </row>
-    <row r="292" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A292" s="4"/>
       <c r="E292" s="7"/>
       <c r="G292" s="7"/>
     </row>
-    <row r="293" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A293" s="4"/>
       <c r="E293" s="7"/>
       <c r="G293" s="7"/>
     </row>
-    <row r="294" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A294" s="4"/>
       <c r="E294" s="7"/>
       <c r="G294" s="7"/>
     </row>
-    <row r="295" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A295" s="4"/>
       <c r="E295" s="7"/>
       <c r="G295" s="7"/>
     </row>
-    <row r="296" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A296" s="4"/>
       <c r="E296" s="7"/>
       <c r="G296" s="7"/>
     </row>
-    <row r="297" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A297" s="4"/>
       <c r="E297" s="7"/>
       <c r="G297" s="7"/>
     </row>
-    <row r="298" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A298" s="4"/>
       <c r="E298" s="7"/>
       <c r="G298" s="7"/>
     </row>
-    <row r="299" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A299" s="4"/>
       <c r="E299" s="7"/>
       <c r="G299" s="7"/>
     </row>
-    <row r="300" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A300" s="4"/>
       <c r="E300" s="7"/>
       <c r="G300" s="7"/>
     </row>
-    <row r="301" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A301" s="4"/>
       <c r="E301" s="7"/>
       <c r="G301" s="7"/>
     </row>
-    <row r="302" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A302" s="4"/>
       <c r="E302" s="7"/>
       <c r="G302" s="7"/>
     </row>
-    <row r="303" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A303" s="4"/>
       <c r="E303" s="7"/>
       <c r="G303" s="7"/>
     </row>
-    <row r="304" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A304" s="4"/>
       <c r="E304" s="7"/>
       <c r="G304" s="7"/>
     </row>
-    <row r="305" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A305" s="4"/>
       <c r="E305" s="7"/>
       <c r="G305" s="7"/>
     </row>
-    <row r="306" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A306" s="4"/>
       <c r="E306" s="7"/>
       <c r="G306" s="7"/>
     </row>
-    <row r="307" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A307" s="4"/>
       <c r="E307" s="7"/>
       <c r="G307" s="7"/>
     </row>
-    <row r="308" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A308" s="4"/>
       <c r="E308" s="7"/>
       <c r="G308" s="7"/>
     </row>
-    <row r="309" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A309" s="4"/>
       <c r="E309" s="7"/>
       <c r="G309" s="7"/>
     </row>
-    <row r="310" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A310" s="4"/>
       <c r="E310" s="7"/>
       <c r="G310" s="7"/>
     </row>
-    <row r="311" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A311" s="4"/>
       <c r="E311" s="7"/>
       <c r="G311" s="7"/>
     </row>
-    <row r="312" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A312" s="4"/>
       <c r="E312" s="7"/>
       <c r="G312" s="7"/>
     </row>
-    <row r="313" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A313" s="4"/>
       <c r="E313" s="7"/>
       <c r="G313" s="7"/>
     </row>
-    <row r="314" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A314" s="4"/>
       <c r="E314" s="7"/>
       <c r="G314" s="7"/>
     </row>
-    <row r="315" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A315" s="4"/>
       <c r="E315" s="7"/>
       <c r="G315" s="7"/>
     </row>
-    <row r="316" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A316" s="4"/>
       <c r="E316" s="7"/>
       <c r="G316" s="7"/>
     </row>
-    <row r="317" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A317" s="4"/>
       <c r="E317" s="7"/>
       <c r="G317" s="7"/>
     </row>
-    <row r="318" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A318" s="4"/>
       <c r="E318" s="7"/>
       <c r="G318" s="7"/>
     </row>
-    <row r="319" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A319" s="4"/>
       <c r="E319" s="7"/>
       <c r="G319" s="7"/>
     </row>
-    <row r="320" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A320" s="4"/>
       <c r="E320" s="7"/>
       <c r="G320" s="7"/>
     </row>
-    <row r="321" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A321" s="4"/>
       <c r="E321" s="7"/>
       <c r="G321" s="7"/>
     </row>
-    <row r="322" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A322" s="4"/>
       <c r="E322" s="7"/>
       <c r="G322" s="7"/>
     </row>
-    <row r="323" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A323" s="4"/>
       <c r="E323" s="7"/>
       <c r="G323" s="7"/>
     </row>
-    <row r="324" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A324" s="4"/>
       <c r="E324" s="7"/>
       <c r="G324" s="7"/>
     </row>
-    <row r="325" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A325" s="4"/>
       <c r="E325" s="7"/>
       <c r="G325" s="7"/>
     </row>
-    <row r="326" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A326" s="4"/>
       <c r="E326" s="7"/>
       <c r="G326" s="7"/>
     </row>
-    <row r="327" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A327" s="4"/>
       <c r="E327" s="7"/>
       <c r="G327" s="7"/>
     </row>
-    <row r="328" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A328" s="4"/>
       <c r="E328" s="7"/>
       <c r="G328" s="7"/>
     </row>
-    <row r="329" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A329" s="4"/>
       <c r="E329" s="7"/>
       <c r="G329" s="7"/>
     </row>
-    <row r="330" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A330" s="4"/>
       <c r="E330" s="7"/>
       <c r="G330" s="7"/>
     </row>
-    <row r="331" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A331" s="4"/>
       <c r="E331" s="7"/>
       <c r="G331" s="7"/>
     </row>
-    <row r="332" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A332" s="4"/>
       <c r="E332" s="7"/>
       <c r="G332" s="7"/>
     </row>
-    <row r="333" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A333" s="4"/>
       <c r="E333" s="7"/>
       <c r="G333" s="7"/>
     </row>
-    <row r="334" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A334" s="4"/>
       <c r="E334" s="7"/>
       <c r="G334" s="7"/>
     </row>
-    <row r="335" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A335" s="4"/>
       <c r="E335" s="7"/>
       <c r="G335" s="7"/>
     </row>
-    <row r="336" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A336" s="4"/>
       <c r="E336" s="7"/>
       <c r="G336" s="7"/>
     </row>
-    <row r="337" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A337" s="4"/>
       <c r="E337" s="7"/>
       <c r="G337" s="7"/>
     </row>
-    <row r="338" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A338" s="4"/>
       <c r="E338" s="7"/>
       <c r="G338" s="7"/>
     </row>
-    <row r="339" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A339" s="4"/>
       <c r="E339" s="7"/>
       <c r="G339" s="7"/>
     </row>
-    <row r="340" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A340" s="4"/>
       <c r="E340" s="7"/>
       <c r="G340" s="7"/>
     </row>
-    <row r="341" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A341" s="4"/>
       <c r="E341" s="7"/>
       <c r="G341" s="7"/>
     </row>
-    <row r="342" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A342" s="4"/>
       <c r="E342" s="7"/>
       <c r="G342" s="7"/>
     </row>
-    <row r="343" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A343" s="4"/>
       <c r="E343" s="7"/>
       <c r="G343" s="7"/>
     </row>
-    <row r="344" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A344" s="4"/>
       <c r="E344" s="7"/>
       <c r="G344" s="7"/>
     </row>
-    <row r="345" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A345" s="4"/>
       <c r="E345" s="7"/>
       <c r="G345" s="7"/>
     </row>
-    <row r="346" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A346" s="4"/>
       <c r="E346" s="7"/>
       <c r="G346" s="7"/>
     </row>
-    <row r="347" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A347" s="4"/>
       <c r="E347" s="7"/>
       <c r="G347" s="7"/>
     </row>
-    <row r="348" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A348" s="4"/>
       <c r="E348" s="7"/>
       <c r="G348" s="7"/>
     </row>
-    <row r="349" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A349" s="4"/>
       <c r="E349" s="7"/>
       <c r="G349" s="7"/>
     </row>
-    <row r="350" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A350" s="4"/>
       <c r="E350" s="7"/>
       <c r="G350" s="7"/>
     </row>
-    <row r="351" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A351" s="4"/>
       <c r="E351" s="7"/>
       <c r="G351" s="7"/>
     </row>
-    <row r="352" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A352" s="4"/>
       <c r="E352" s="7"/>
       <c r="G352" s="7"/>
     </row>
-    <row r="353" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A353" s="4"/>
       <c r="E353" s="7"/>
       <c r="G353" s="7"/>
     </row>
-    <row r="354" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A354" s="4"/>
       <c r="E354" s="7"/>
       <c r="G354" s="7"/>
     </row>
-    <row r="355" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A355" s="4"/>
       <c r="E355" s="7"/>
       <c r="G355" s="7"/>
     </row>
-    <row r="356" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A356" s="4"/>
       <c r="E356" s="7"/>
       <c r="G356" s="7"/>
     </row>
-    <row r="357" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A357" s="4"/>
       <c r="E357" s="7"/>
       <c r="G357" s="7"/>
     </row>
-    <row r="358" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A358" s="4"/>
       <c r="E358" s="7"/>
       <c r="G358" s="7"/>
     </row>
-    <row r="359" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A359" s="4"/>
       <c r="E359" s="7"/>
       <c r="G359" s="7"/>
     </row>
-    <row r="360" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A360" s="4"/>
       <c r="E360" s="7"/>
       <c r="G360" s="7"/>
     </row>
-    <row r="361" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A361" s="4"/>
       <c r="E361" s="7"/>
       <c r="G361" s="7"/>
     </row>
-    <row r="362" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A362" s="4"/>
       <c r="E362" s="7"/>
       <c r="G362" s="7"/>
     </row>
-    <row r="363" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A363" s="4"/>
       <c r="E363" s="7"/>
       <c r="G363" s="7"/>
     </row>
-    <row r="364" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A364" s="4"/>
       <c r="E364" s="7"/>
       <c r="G364" s="7"/>
     </row>
-    <row r="365" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A365" s="4"/>
       <c r="E365" s="7"/>
       <c r="G365" s="7"/>
     </row>
-    <row r="366" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A366" s="4"/>
       <c r="E366" s="7"/>
       <c r="G366" s="7"/>
     </row>
-    <row r="367" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A367" s="4"/>
       <c r="E367" s="7"/>
       <c r="G367" s="7"/>
     </row>
-    <row r="368" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A368" s="4"/>
       <c r="E368" s="7"/>
       <c r="G368" s="7"/>
     </row>
-    <row r="369" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A369" s="4"/>
       <c r="E369" s="7"/>
       <c r="G369" s="7"/>
     </row>
-    <row r="370" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A370" s="4"/>
       <c r="E370" s="7"/>
       <c r="G370" s="7"/>
     </row>
-    <row r="371" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A371" s="4"/>
       <c r="E371" s="7"/>
       <c r="G371" s="7"/>
     </row>
-    <row r="372" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A372" s="4"/>
       <c r="E372" s="7"/>
       <c r="G372" s="7"/>
     </row>
-    <row r="373" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A373" s="4"/>
       <c r="E373" s="7"/>
       <c r="G373" s="7"/>

--- a/business_analysis/AI/DailyChatFlow.xlsx
+++ b/business_analysis/AI/DailyChatFlow.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="wellbeing_scores_2099_students" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -731,7 +731,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1023,7 +1023,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1112,11 +1112,14 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1511,7 +1514,7 @@
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="32" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="10"/>
@@ -1525,7 +1528,7 @@
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="32" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="5">
